--- a/sheets/조재수대금교본/검수/한오백년 카덴자.xlsx
+++ b/sheets/조재수대금교본/검수/한오백년 카덴자.xlsx
@@ -1458,8 +1458,7 @@
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -1483,7 +1482,7 @@
       <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ʒ
+          <t xml:space="preserve">湳
 –</t>
         </is>
       </c>
@@ -1500,7 +1499,7 @@
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–㳞ʒ</t>
+–㳞</t>
         </is>
       </c>
       <c r="E5" s="24"/>
@@ -1518,12 +1517,7 @@
         </is>
       </c>
       <c r="E6" s="22"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-Z</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="22"/>
     </row>
     <row r="7" ht="96.05" customHeight="true">
@@ -1532,15 +1526,14 @@
       <c r="C7" s="23"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞淋∧
-–⌝</t>
+          <t xml:space="preserve">㳞淋
+–</t>
         </is>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z
-–淋</t>
+          <t xml:space="preserve">–淋</t>
         </is>
       </c>
       <c r="G7" s="23"/>
@@ -1552,7 +1545,7 @@
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="E8" s="24"/>
@@ -1570,8 +1563,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ʒ
-ﾉ
+          <t xml:space="preserve">㳞
 汰潢</t>
         </is>
       </c>
@@ -1590,14 +1582,13 @@
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="G10" s="23"/>
@@ -1615,7 +1606,7 @@
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -1626,7 +1617,7 @@
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
+          <t xml:space="preserve">汰
 㳞</t>
         </is>
       </c>
@@ -1646,7 +1637,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="E13" s="23"/>

--- a/sheets/조재수대금교본/검수/한오백년 카덴자.xlsx
+++ b/sheets/조재수대금교본/검수/한오백년 카덴자.xlsx
@@ -1482,7 +1482,7 @@
       <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
+          <t xml:space="preserve">湳ʒ
 –</t>
         </is>
       </c>
@@ -1499,7 +1499,7 @@
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–㳞</t>
+–㳞ʒ</t>
         </is>
       </c>
       <c r="E5" s="24"/>
@@ -1517,7 +1517,12 @@
         </is>
       </c>
       <c r="E6" s="22"/>
-      <c r="F6" s="21"/>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+Z</t>
+        </is>
+      </c>
       <c r="G6" s="22"/>
     </row>
     <row r="7" ht="96.05" customHeight="true">
@@ -1526,14 +1531,15 @@
       <c r="C7" s="23"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞淋
-–</t>
+          <t xml:space="preserve">㳞淋∧
+–⌝</t>
         </is>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–淋</t>
+          <t xml:space="preserve">Z
+–淋</t>
         </is>
       </c>
       <c r="G7" s="23"/>
@@ -1545,7 +1551,7 @@
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="E8" s="24"/>
@@ -1563,7 +1569,8 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ʒ
+ﾉ
 汰潢</t>
         </is>
       </c>
@@ -1588,7 +1595,7 @@
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="G10" s="23"/>
@@ -1606,7 +1613,7 @@
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -1617,7 +1624,7 @@
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰∧
 㳞</t>
         </is>
       </c>
@@ -1637,7 +1644,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="E13" s="23"/>

--- a/sheets/조재수대금교본/검수/한오백년 카덴자.xlsx
+++ b/sheets/조재수대금교본/검수/한오백년 카덴자.xlsx
@@ -1427,11 +1427,11 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
   </cols>
   <sheetData>
